--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108486</v>
+        <v>108491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108491</v>
+        <v>108512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108512</v>
+        <v>108513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108513</v>
+        <v>108518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108518</v>
+        <v>108521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108521</v>
+        <v>108527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108527</v>
+        <v>108528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108528</v>
+        <v>108540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108540</v>
+        <v>108541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108541</v>
+        <v>108544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108544</v>
+        <v>108546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34344-2026 artfynd.xlsx
+++ b/artfynd/A 34344-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951540</v>
       </c>
       <c r="B2" t="n">
-        <v>108546</v>
+        <v>108550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
